--- a/tasks/finalpool/canvas-faculty-workload-review/groundtruth_workspace/Faculty_Workload.xlsx
+++ b/tasks/finalpool/canvas-faculty-workload-review/groundtruth_workspace/Faculty_Workload.xlsx
@@ -1405,7 +1405,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1113</v>
+        <v>748</v>
       </c>
     </row>
     <row r="3">
@@ -1418,10 +1418,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>16596</v>
+        <v>7909</v>
       </c>
     </row>
     <row r="4">
@@ -1437,7 +1437,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>6370</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="5">
@@ -1453,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>11834</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="6">
@@ -1469,7 +1469,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4122</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="7">
@@ -1485,7 +1485,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>17971</v>
+        <v>7762</v>
       </c>
     </row>
     <row r="8">
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4984</v>
+        <v>2534</v>
       </c>
     </row>
   </sheetData>
